--- a/Интеллектуальный анализ данных/Лабораторные работы/ExpData.xlsx
+++ b/Интеллектуальный анализ данных/Лабораторные работы/ExpData.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Honor\OneDrive\Рабочий стол\Lessons\6-semestr\Интеллектуальный анализ данных\Лабораторные работы\ЛР3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\6 semestr\Интеллектуальный анализ данных\Лабораторные работы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5547C9B9-94C6-4757-BD2B-DBBFB6822D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC6F899-4D2D-4D36-B159-461D8EC9DF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1824" yWindow="2484" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1155" yWindow="60" windowWidth="25425" windowHeight="11340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" r:id="rId1"/>
-    <sheet name="Страны_СредняяЗП" sheetId="2" r:id="rId2"/>
-    <sheet name="Страны_СредняяЗП_в_Колонку" sheetId="3" r:id="rId3"/>
+    <sheet name="Данные с исключённым ВВП" sheetId="4" r:id="rId2"/>
+    <sheet name="Страны_СредняяЗП" sheetId="2" r:id="rId3"/>
+    <sheet name="Страны_СредняяЗП_в_Колонку" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="305">
   <si>
     <t>Страна</t>
   </si>
@@ -1051,7 +1052,27 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{A36A347A-F292-4748-875D-9062A2E8BF18}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1349,17 +1370,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G110"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="42.33203125" customWidth="1"/>
-    <col min="6" max="6" width="17.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="42.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1382,7 +1403,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>39</v>
       </c>
@@ -1405,7 +1426,7 @@
         <v>47.668300000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
@@ -1428,7 +1449,7 @@
         <v>42.214599999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1451,7 +1472,7 @@
         <v>22.1432</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -1474,7 +1495,7 @@
         <v>24.020399999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>56</v>
       </c>
@@ -1497,7 +1518,7 @@
         <v>44.591700000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>34</v>
       </c>
@@ -1520,7 +1541,7 @@
         <v>14.273099999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>41</v>
       </c>
@@ -1543,7 +1564,7 @@
         <v>11.8727</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>51</v>
       </c>
@@ -1566,7 +1587,7 @@
         <v>38.947499999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>76</v>
       </c>
@@ -1589,7 +1610,7 @@
         <v>4.6841999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>73</v>
       </c>
@@ -1612,7 +1633,7 @@
         <v>17.5046</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>67</v>
       </c>
@@ -1635,7 +1656,7 @@
         <v>18.9941</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>64</v>
       </c>
@@ -1658,7 +1679,7 @@
         <v>125.4355</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>50</v>
       </c>
@@ -1681,7 +1702,7 @@
         <v>16.008900000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>72</v>
       </c>
@@ -1704,7 +1725,7 @@
         <v>10.260300000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
@@ -1727,7 +1748,7 @@
         <v>61.3264</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>65</v>
       </c>
@@ -1750,7 +1771,7 @@
         <v>4.3868</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>69</v>
       </c>
@@ -1773,7 +1794,7 @@
         <v>4.2523</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
@@ -1796,7 +1817,7 @@
         <v>15.1922</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>63</v>
       </c>
@@ -1819,7 +1840,7 @@
         <v>3.8130999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
@@ -1842,7 +1863,7 @@
         <v>4.6158000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>26</v>
       </c>
@@ -1865,7 +1886,7 @@
         <v>6.8696999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>43</v>
       </c>
@@ -1888,7 +1909,7 @@
         <v>1.6366000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>6</v>
       </c>
@@ -1911,7 +1932,7 @@
         <v>5.1379999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
@@ -1934,7 +1955,7 @@
         <v>5.7367999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>75</v>
       </c>
@@ -1957,7 +1978,7 @@
         <v>2.9946999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>66</v>
       </c>
@@ -1980,7 +2001,7 @@
         <v>6.5157999999999996</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
@@ -2003,7 +2024,7 @@
         <v>7.0401999999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>11</v>
       </c>
@@ -2026,7 +2047,7 @@
         <v>20.5472</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
@@ -2049,7 +2070,7 @@
         <v>23.237500000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>54</v>
       </c>
@@ -2072,7 +2093,7 @@
         <v>12.550700000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
@@ -2095,7 +2116,7 @@
         <v>4.2380000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -2118,7 +2139,7 @@
         <v>4.4191000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>20</v>
       </c>
@@ -2141,7 +2162,7 @@
         <v>18.1432</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>44</v>
       </c>
@@ -2164,7 +2185,7 @@
         <v>15.417299999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>70</v>
       </c>
@@ -2187,7 +2208,7 @@
         <v>15.570499999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
@@ -2210,7 +2231,7 @@
         <v>6.2824</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
@@ -2233,7 +2254,7 @@
         <v>7.7009999999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>61</v>
       </c>
@@ -2256,7 +2277,7 @@
         <v>43.774999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>7</v>
       </c>
@@ -2279,7 +2300,7 @@
         <v>4.5247000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>22</v>
       </c>
@@ -2302,7 +2323,7 @@
         <v>16.164200000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>14</v>
       </c>
@@ -2325,7 +2346,7 @@
         <v>11.299300000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>27</v>
       </c>
@@ -2348,7 +2369,7 @@
         <v>6.4661</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>42</v>
       </c>
@@ -2371,7 +2392,7 @@
         <v>14.3863</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>59</v>
       </c>
@@ -2394,7 +2415,7 @@
         <v>18.075199999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2417,7 +2438,7 @@
         <v>8.5898000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>57</v>
       </c>
@@ -2440,7 +2461,7 @@
         <v>5.3072999999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>19</v>
       </c>
@@ -2463,7 +2484,7 @@
         <v>24.271100000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2486,7 +2507,7 @@
         <v>6.8183999999999996</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>17</v>
       </c>
@@ -2509,7 +2530,7 @@
         <v>14.563700000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>49</v>
       </c>
@@ -2532,7 +2553,7 @@
         <v>2.2035999999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>71</v>
       </c>
@@ -2555,7 +2576,7 @@
         <v>32.428699999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>47</v>
       </c>
@@ -2578,7 +2599,7 @@
         <v>19.080300000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>24</v>
       </c>
@@ -2601,7 +2622,7 @@
         <v>7.7512999999999996</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>28</v>
       </c>
@@ -2624,7 +2645,7 @@
         <v>12.9817</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>45</v>
       </c>
@@ -2647,7 +2668,7 @@
         <v>16.587599999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>48</v>
       </c>
@@ -2670,7 +2691,7 @@
         <v>12.830500000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>68</v>
       </c>
@@ -2693,7 +2714,7 @@
         <v>24.767600000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>30</v>
       </c>
@@ -2716,7 +2737,7 @@
         <v>30.696200000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>46</v>
       </c>
@@ -2739,7 +2760,7 @@
         <v>6.5964</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>62</v>
       </c>
@@ -2762,7 +2783,7 @@
         <v>64.125100000000003</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>52</v>
       </c>
@@ -2785,7 +2806,7 @@
         <v>10.0938</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>33</v>
       </c>
@@ -2808,7 +2829,7 @@
         <v>18.5213</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>58</v>
       </c>
@@ -2831,7 +2852,7 @@
         <v>11.868499999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>74</v>
       </c>
@@ -2854,7 +2875,7 @@
         <v>11.0524</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>55</v>
       </c>
@@ -2877,7 +2898,7 @@
         <v>84.392899999999997</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>23</v>
       </c>
@@ -2900,7 +2921,7 @@
         <v>8.9933999999999994</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>29</v>
       </c>
@@ -2923,7 +2944,7 @@
         <v>10.960699999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>10</v>
       </c>
@@ -2946,7 +2967,7 @@
         <v>30.5215</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>21</v>
       </c>
@@ -2969,7 +2990,7 @@
         <v>10.133800000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>3</v>
       </c>
@@ -2992,7 +3013,7 @@
         <v>14.847200000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>60</v>
       </c>
@@ -3015,7 +3036,7 @@
         <v>14.7935</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3038,7 +3059,7 @@
         <v>29.537600000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>9</v>
       </c>
@@ -3061,7 +3082,7 @@
         <v>33.941499999999998</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>37</v>
       </c>
@@ -3084,245 +3105,245 @@
         <v>7.3418999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -3334,10 +3355,10 @@
     <sortCondition ref="G2:G148"/>
   </sortState>
   <conditionalFormatting sqref="G1 B1:F1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>#N/A</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="#Н/Д">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="#Н/Д">
       <formula>NOT(ISERROR(SEARCH("#Н/Д",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3347,11 +3368,1529 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{226347C7-C38F-4C9A-8B9E-588CAFBE6ADF}">
+  <dimension ref="A1:F75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="7">
+        <v>78.64</v>
+      </c>
+      <c r="C2" s="7">
+        <v>8.85</v>
+      </c>
+      <c r="D2" s="7">
+        <v>61.06</v>
+      </c>
+      <c r="E2" s="7">
+        <v>102.69132</v>
+      </c>
+      <c r="F2" s="5">
+        <v>47.668300000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="7">
+        <v>82.55</v>
+      </c>
+      <c r="C3" s="7">
+        <v>3.54</v>
+      </c>
+      <c r="D3" s="7">
+        <v>73.319999999999993</v>
+      </c>
+      <c r="E3" s="7">
+        <v>105.24057000000001</v>
+      </c>
+      <c r="F3" s="5">
+        <v>42.214599999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7">
+        <v>68.430000000000007</v>
+      </c>
+      <c r="C4" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="D4" s="7">
+        <v>56.74</v>
+      </c>
+      <c r="E4" s="7">
+        <v>106.13681</v>
+      </c>
+      <c r="F4" s="5">
+        <v>22.1432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="7">
+        <v>74.510000000000005</v>
+      </c>
+      <c r="C5" s="7">
+        <v>14.65</v>
+      </c>
+      <c r="D5" s="7">
+        <v>64.510000000000005</v>
+      </c>
+      <c r="E5" s="7">
+        <v>109.15422</v>
+      </c>
+      <c r="F5" s="5">
+        <v>24.020399999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="7">
+        <v>81.96</v>
+      </c>
+      <c r="C6" s="7">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="D6" s="7">
+        <v>72.05</v>
+      </c>
+      <c r="E6" s="7">
+        <v>111.34717999999999</v>
+      </c>
+      <c r="F6" s="5">
+        <v>44.591700000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="7">
+        <v>77.349999999999994</v>
+      </c>
+      <c r="C7" s="7">
+        <v>15.01</v>
+      </c>
+      <c r="D7" s="7">
+        <v>44.53</v>
+      </c>
+      <c r="E7" s="7">
+        <v>114.50292</v>
+      </c>
+      <c r="F7" s="5">
+        <v>14.273099999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="7">
+        <v>73</v>
+      </c>
+      <c r="C8" s="7">
+        <v>18.77</v>
+      </c>
+      <c r="D8" s="7">
+        <v>50.57</v>
+      </c>
+      <c r="E8" s="7">
+        <v>128.86314999999999</v>
+      </c>
+      <c r="F8" s="5">
+        <v>11.8727</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="7">
+        <v>75.22</v>
+      </c>
+      <c r="C9" s="7">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="D9" s="7">
+        <v>54.28</v>
+      </c>
+      <c r="E9" s="7">
+        <v>137.09370999999999</v>
+      </c>
+      <c r="F9" s="5">
+        <v>38.947499999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="7">
+        <v>60.87</v>
+      </c>
+      <c r="C10" s="7">
+        <v>53.35</v>
+      </c>
+      <c r="D10" s="7">
+        <v>26.94</v>
+      </c>
+      <c r="E10" s="7">
+        <v>14.87153</v>
+      </c>
+      <c r="F10" s="5">
+        <v>4.6841999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="7">
+        <v>75.75</v>
+      </c>
+      <c r="C11" s="7">
+        <v>20.95</v>
+      </c>
+      <c r="D11" s="7">
+        <v>54.67</v>
+      </c>
+      <c r="E11" s="7">
+        <v>140.60368</v>
+      </c>
+      <c r="F11" s="5">
+        <v>17.5046</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="7">
+        <v>78.72</v>
+      </c>
+      <c r="C12" s="7">
+        <v>8.65</v>
+      </c>
+      <c r="D12" s="7">
+        <v>60.22</v>
+      </c>
+      <c r="E12" s="7">
+        <v>146.59352999999999</v>
+      </c>
+      <c r="F12" s="5">
+        <v>18.9941</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="7">
+        <v>83.94</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2.23</v>
+      </c>
+      <c r="D13" s="7">
+        <v>63.78</v>
+      </c>
+      <c r="E13" s="7">
+        <v>148.61811</v>
+      </c>
+      <c r="F13" s="5">
+        <v>125.4355</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="7">
+        <v>74.69</v>
+      </c>
+      <c r="C14" s="7">
+        <v>16.510000000000002</v>
+      </c>
+      <c r="D14" s="7">
+        <v>62.41</v>
+      </c>
+      <c r="E14" s="7">
+        <v>156.74615</v>
+      </c>
+      <c r="F14" s="5">
+        <v>16.008900000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="7">
+        <v>67.47</v>
+      </c>
+      <c r="C15" s="7">
+        <v>13.95</v>
+      </c>
+      <c r="D15" s="7">
+        <v>61.54</v>
+      </c>
+      <c r="E15" s="7">
+        <v>16.767320000000002</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10.260300000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="7">
+        <v>82.87</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3.05</v>
+      </c>
+      <c r="D16" s="7">
+        <v>59.03</v>
+      </c>
+      <c r="E16" s="7">
+        <v>164.87826000000001</v>
+      </c>
+      <c r="F16" s="5">
+        <v>61.3264</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="7">
+        <v>61.27</v>
+      </c>
+      <c r="C17" s="7">
+        <v>107.78</v>
+      </c>
+      <c r="D17" s="7">
+        <v>34.47</v>
+      </c>
+      <c r="E17" s="7">
+        <v>17.919219999999999</v>
+      </c>
+      <c r="F17" s="5">
+        <v>4.3868</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="7">
+        <v>66.61</v>
+      </c>
+      <c r="C18" s="7">
+        <v>48.72</v>
+      </c>
+      <c r="D18" s="7">
+        <v>36.4</v>
+      </c>
+      <c r="E18" s="7">
+        <v>19.74025</v>
+      </c>
+      <c r="F18" s="5">
+        <v>4.2523</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7">
+        <v>77.7</v>
+      </c>
+      <c r="C19" s="7">
+        <v>7.35</v>
+      </c>
+      <c r="D19" s="7">
+        <v>51.44</v>
+      </c>
+      <c r="E19" s="7">
+        <v>207.53029000000001</v>
+      </c>
+      <c r="F19" s="5">
+        <v>15.1922</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="7">
+        <v>69</v>
+      </c>
+      <c r="C20" s="7">
+        <v>40.43</v>
+      </c>
+      <c r="D20" s="7">
+        <v>32.68</v>
+      </c>
+      <c r="E20" s="7">
+        <v>25.147749999999998</v>
+      </c>
+      <c r="F20" s="5">
+        <v>3.8130999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="7">
+        <v>64.31</v>
+      </c>
+      <c r="C21" s="7">
+        <v>114.08</v>
+      </c>
+      <c r="D21" s="7">
+        <v>42.66</v>
+      </c>
+      <c r="E21" s="7">
+        <v>25.221609999999998</v>
+      </c>
+      <c r="F21" s="5">
+        <v>4.6158000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="7">
+        <v>60.84</v>
+      </c>
+      <c r="C22" s="7">
+        <v>95.49</v>
+      </c>
+      <c r="D22" s="7">
+        <v>47.68</v>
+      </c>
+      <c r="E22" s="7">
+        <v>26.676369999999999</v>
+      </c>
+      <c r="F22" s="5">
+        <v>6.8696999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="7">
+        <v>64.790000000000006</v>
+      </c>
+      <c r="C23" s="7">
+        <v>50.26</v>
+      </c>
+      <c r="D23" s="7">
+        <v>43.39</v>
+      </c>
+      <c r="E23" s="7">
+        <v>28.23752</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1.6366000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="7">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="C24" s="7">
+        <v>85.91</v>
+      </c>
+      <c r="D24" s="7">
+        <v>49.76</v>
+      </c>
+      <c r="E24" s="7">
+        <v>30.54665</v>
+      </c>
+      <c r="F24" s="5">
+        <v>5.1379999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="7">
+        <v>65.67</v>
+      </c>
+      <c r="C25" s="7">
+        <v>44.71</v>
+      </c>
+      <c r="D25" s="7">
+        <v>49.67</v>
+      </c>
+      <c r="E25" s="7">
+        <v>30.817319999999999</v>
+      </c>
+      <c r="F25" s="5">
+        <v>5.7367999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="7">
+        <v>62.77</v>
+      </c>
+      <c r="C26" s="7">
+        <v>61.11</v>
+      </c>
+      <c r="D26" s="7">
+        <v>33.07</v>
+      </c>
+      <c r="E26" s="7">
+        <v>31.205960000000001</v>
+      </c>
+      <c r="F26" s="5">
+        <v>2.9946999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="7">
+        <v>57.43</v>
+      </c>
+      <c r="C27" s="7">
+        <v>46.81</v>
+      </c>
+      <c r="D27" s="7">
+        <v>43.96</v>
+      </c>
+      <c r="E27" s="7">
+        <v>31.24578</v>
+      </c>
+      <c r="F27" s="5">
+        <v>6.5157999999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="7">
+        <v>68.83</v>
+      </c>
+      <c r="C28" s="7">
+        <v>61.37</v>
+      </c>
+      <c r="D28" s="7">
+        <v>46.09</v>
+      </c>
+      <c r="E28" s="7">
+        <v>31.390509999999999</v>
+      </c>
+      <c r="F28" s="5">
+        <v>7.0401999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="7">
+        <v>72.319999999999993</v>
+      </c>
+      <c r="C29" s="7">
+        <v>2.91</v>
+      </c>
+      <c r="D29" s="7">
+        <v>58.21</v>
+      </c>
+      <c r="E29" s="7">
+        <v>33.930259999999997</v>
+      </c>
+      <c r="F29" s="5">
+        <v>20.5472</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="7">
+        <v>75.2</v>
+      </c>
+      <c r="C30" s="7">
+        <v>8.74</v>
+      </c>
+      <c r="D30" s="7">
+        <v>60.86</v>
+      </c>
+      <c r="E30" s="7">
+        <v>34.50526</v>
+      </c>
+      <c r="F30" s="5">
+        <v>23.237500000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="7">
+        <v>73.08</v>
+      </c>
+      <c r="C31" s="7">
+        <v>16.03</v>
+      </c>
+      <c r="D31" s="7">
+        <v>61.13</v>
+      </c>
+      <c r="E31" s="7">
+        <v>39.794629999999998</v>
+      </c>
+      <c r="F31" s="5">
+        <v>12.550700000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="7">
+        <v>66.23</v>
+      </c>
+      <c r="C32" s="7">
+        <v>42.18</v>
+      </c>
+      <c r="D32" s="7">
+        <v>46.19</v>
+      </c>
+      <c r="E32" s="7">
+        <v>41.202579999999998</v>
+      </c>
+      <c r="F32" s="5">
+        <v>4.2380000000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="7">
+        <v>52.27</v>
+      </c>
+      <c r="C33" s="7">
+        <v>89.5</v>
+      </c>
+      <c r="D33" s="7">
+        <v>35.119999999999997</v>
+      </c>
+      <c r="E33" s="7">
+        <v>42.254519999999999</v>
+      </c>
+      <c r="F33" s="5">
+        <v>4.4191000000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="7">
+        <v>72.5</v>
+      </c>
+      <c r="C34" s="7">
+        <v>33.74</v>
+      </c>
+      <c r="D34" s="7">
+        <v>60.04</v>
+      </c>
+      <c r="E34" s="7">
+        <v>42.916350000000001</v>
+      </c>
+      <c r="F34" s="5">
+        <v>18.1432</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="7">
+        <v>71.48</v>
+      </c>
+      <c r="C35" s="7">
+        <v>13.67</v>
+      </c>
+      <c r="D35" s="7">
+        <v>64.319999999999993</v>
+      </c>
+      <c r="E35" s="7">
+        <v>43.501379999999997</v>
+      </c>
+      <c r="F35" s="5">
+        <v>15.417299999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="7">
+        <v>71.89</v>
+      </c>
+      <c r="C36" s="7">
+        <v>7.03</v>
+      </c>
+      <c r="D36" s="7">
+        <v>47.02</v>
+      </c>
+      <c r="E36" s="7">
+        <v>43.817999999999998</v>
+      </c>
+      <c r="F36" s="5">
+        <v>15.570499999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7">
+        <v>71.77</v>
+      </c>
+      <c r="C37" s="7">
+        <v>17.54</v>
+      </c>
+      <c r="D37" s="7">
+        <v>56.85</v>
+      </c>
+      <c r="E37" s="7">
+        <v>44.591720000000002</v>
+      </c>
+      <c r="F37" s="5">
+        <v>6.2824</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="7">
+        <v>69.650000000000006</v>
+      </c>
+      <c r="C38" s="6">
+        <v>23</v>
+      </c>
+      <c r="D38" s="7">
+        <v>53.47</v>
+      </c>
+      <c r="E38" s="7">
+        <v>44.717869999999998</v>
+      </c>
+      <c r="F38" s="5">
+        <v>7.7009999999999996</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="7">
+        <v>74.38</v>
+      </c>
+      <c r="C39" s="7">
+        <v>6.75</v>
+      </c>
+      <c r="D39" s="7">
+        <v>61.3</v>
+      </c>
+      <c r="E39" s="7">
+        <v>45.5625</v>
+      </c>
+      <c r="F39" s="5">
+        <v>43.774999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="7">
+        <v>61.36</v>
+      </c>
+      <c r="C40" s="7">
+        <v>84.9</v>
+      </c>
+      <c r="D40" s="7">
+        <v>47.41</v>
+      </c>
+      <c r="E40" s="7">
+        <v>46.844619999999999</v>
+      </c>
+      <c r="F40" s="5">
+        <v>4.5247000000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="7">
+        <v>71.290000000000006</v>
+      </c>
+      <c r="C41" s="7">
+        <v>12.93</v>
+      </c>
+      <c r="D41" s="7">
+        <v>58.09</v>
+      </c>
+      <c r="E41" s="7">
+        <v>50.638750000000002</v>
+      </c>
+      <c r="F41" s="5">
+        <v>16.164200000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="7">
+        <v>62.42</v>
+      </c>
+      <c r="C42" s="7">
+        <v>44.96</v>
+      </c>
+      <c r="D42" s="7">
+        <v>34.71</v>
+      </c>
+      <c r="E42" s="7">
+        <v>52.373449999999998</v>
+      </c>
+      <c r="F42" s="5">
+        <v>11.299300000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" s="7">
+        <v>65.55</v>
+      </c>
+      <c r="C43" s="7">
+        <v>49.39</v>
+      </c>
+      <c r="D43" s="7">
+        <v>51.64</v>
+      </c>
+      <c r="E43" s="7">
+        <v>52.939369999999997</v>
+      </c>
+      <c r="F43" s="5">
+        <v>6.4661</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="7">
+        <v>73.52</v>
+      </c>
+      <c r="C44" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="D44" s="7">
+        <v>58.03</v>
+      </c>
+      <c r="E44" s="7">
+        <v>53.887230000000002</v>
+      </c>
+      <c r="F44" s="5">
+        <v>14.3863</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="7">
+        <v>76.150000000000006</v>
+      </c>
+      <c r="C45" s="7">
+        <v>18.760000000000002</v>
+      </c>
+      <c r="D45" s="7">
+        <v>56.53</v>
+      </c>
+      <c r="E45" s="7">
+        <v>54.177810000000001</v>
+      </c>
+      <c r="F45" s="5">
+        <v>18.075199999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="7">
+        <v>72.45</v>
+      </c>
+      <c r="C46" s="7">
+        <v>10.93</v>
+      </c>
+      <c r="D46" s="7">
+        <v>54.88</v>
+      </c>
+      <c r="E46" s="7">
+        <v>54.385170000000002</v>
+      </c>
+      <c r="F46" s="5">
+        <v>8.5898000000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="7">
+        <v>65.38</v>
+      </c>
+      <c r="C47" s="7">
+        <v>65.23</v>
+      </c>
+      <c r="D47" s="7">
+        <v>44.43</v>
+      </c>
+      <c r="E47" s="7">
+        <v>54.526389999999999</v>
+      </c>
+      <c r="F47" s="5">
+        <v>5.3072999999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="7">
+        <v>79.92</v>
+      </c>
+      <c r="C48" s="7">
+        <v>7.92</v>
+      </c>
+      <c r="D48" s="7">
+        <v>69.98</v>
+      </c>
+      <c r="E48" s="7">
+        <v>54.865789999999997</v>
+      </c>
+      <c r="F48" s="5">
+        <v>24.271100000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="7">
+        <v>73.7</v>
+      </c>
+      <c r="C49" s="7">
+        <v>29.1</v>
+      </c>
+      <c r="D49" s="7">
+        <v>51.14</v>
+      </c>
+      <c r="E49" s="7">
+        <v>57.763060000000003</v>
+      </c>
+      <c r="F49" s="5">
+        <v>6.8183999999999996</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="7">
+        <v>78.12</v>
+      </c>
+      <c r="C50" s="7">
+        <v>13.14</v>
+      </c>
+      <c r="D50" s="7">
+        <v>63.5</v>
+      </c>
+      <c r="E50" s="7">
+        <v>58.278440000000003</v>
+      </c>
+      <c r="F50" s="5">
+        <v>14.563700000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="7">
+        <v>58.39</v>
+      </c>
+      <c r="C51" s="7">
+        <v>70.44</v>
+      </c>
+      <c r="D51" s="7">
+        <v>49.32</v>
+      </c>
+      <c r="E51" s="7">
+        <v>59.025269999999999</v>
+      </c>
+      <c r="F51" s="5">
+        <v>2.2035999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" s="7">
+        <v>78.45</v>
+      </c>
+      <c r="C52" s="7">
+        <v>5.36</v>
+      </c>
+      <c r="D52" s="7">
+        <v>66</v>
+      </c>
+      <c r="E52" s="7">
+        <v>59.126899999999999</v>
+      </c>
+      <c r="F52" s="5">
+        <v>32.428699999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" s="7">
+        <v>75.09</v>
+      </c>
+      <c r="C53" s="7">
+        <v>2.37</v>
+      </c>
+      <c r="D53" s="7">
+        <v>53.86</v>
+      </c>
+      <c r="E53" s="7">
+        <v>59.356900000000003</v>
+      </c>
+      <c r="F53" s="5">
+        <v>19.080300000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="7">
+        <v>72.7</v>
+      </c>
+      <c r="C54" s="7">
+        <v>9.25</v>
+      </c>
+      <c r="D54" s="7">
+        <v>48.92</v>
+      </c>
+      <c r="E54" s="7">
+        <v>61.016669999999998</v>
+      </c>
+      <c r="F54" s="5">
+        <v>7.7512999999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" s="7">
+        <v>71.25</v>
+      </c>
+      <c r="C55" s="7">
+        <v>23.67</v>
+      </c>
+      <c r="D55" s="7">
+        <v>62.62</v>
+      </c>
+      <c r="E55" s="7">
+        <v>62.752429999999997</v>
+      </c>
+      <c r="F55" s="5">
+        <v>12.9817</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" s="7">
+        <v>72.33</v>
+      </c>
+      <c r="C56" s="7">
+        <v>6.47</v>
+      </c>
+      <c r="D56" s="7">
+        <v>50.15</v>
+      </c>
+      <c r="E56" s="7">
+        <v>65.179130000000001</v>
+      </c>
+      <c r="F56" s="5">
+        <v>16.587599999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B57" s="7">
+        <v>68.38</v>
+      </c>
+      <c r="C57" s="7">
+        <v>15.35</v>
+      </c>
+      <c r="D57" s="7">
+        <v>55.63</v>
+      </c>
+      <c r="E57" s="7">
+        <v>65.363439999999997</v>
+      </c>
+      <c r="F57" s="5">
+        <v>12.830500000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="7">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="C58" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="D58" s="7">
+        <v>48.72</v>
+      </c>
+      <c r="E58" s="7">
+        <v>67.478089999999995</v>
+      </c>
+      <c r="F58" s="5">
+        <v>24.767600000000002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" s="7">
+        <v>75.88</v>
+      </c>
+      <c r="C59" s="7">
+        <v>3.78</v>
+      </c>
+      <c r="D59" s="7">
+        <v>60</v>
+      </c>
+      <c r="E59" s="7">
+        <v>68.769679999999994</v>
+      </c>
+      <c r="F59" s="5">
+        <v>30.696200000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60" s="7">
+        <v>69.66</v>
+      </c>
+      <c r="C60" s="7">
+        <v>43.61</v>
+      </c>
+      <c r="D60" s="7">
+        <v>44.34</v>
+      </c>
+      <c r="E60" s="7">
+        <v>69.204639999999998</v>
+      </c>
+      <c r="F60" s="5">
+        <v>6.5964</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="7">
+        <v>70.41</v>
+      </c>
+      <c r="C61" s="7">
+        <v>5.19</v>
+      </c>
+      <c r="D61" s="7">
+        <v>54.41</v>
+      </c>
+      <c r="E61" s="7">
+        <v>69.92953</v>
+      </c>
+      <c r="F61" s="5">
+        <v>64.125100000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="7">
+        <v>64.97</v>
+      </c>
+      <c r="C62" s="7">
+        <v>40.46</v>
+      </c>
+      <c r="D62" s="7">
+        <v>44.36</v>
+      </c>
+      <c r="E62" s="7">
+        <v>71.539259999999999</v>
+      </c>
+      <c r="F62" s="5">
+        <v>10.0938</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" s="7">
+        <v>76.36</v>
+      </c>
+      <c r="C63" s="7">
+        <v>13.2</v>
+      </c>
+      <c r="D63" s="7">
+        <v>63.09</v>
+      </c>
+      <c r="E63" s="7">
+        <v>71.776740000000004</v>
+      </c>
+      <c r="F63" s="5">
+        <v>18.5213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B64" s="7">
+        <v>77.62</v>
+      </c>
+      <c r="C64" s="7">
+        <v>12.78</v>
+      </c>
+      <c r="D64" s="7">
+        <v>59.99</v>
+      </c>
+      <c r="E64" s="7">
+        <v>73.438630000000003</v>
+      </c>
+      <c r="F64" s="5">
+        <v>11.868499999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" s="7">
+        <v>64.239999999999995</v>
+      </c>
+      <c r="C65" s="7">
+        <v>26.69</v>
+      </c>
+      <c r="D65" s="7">
+        <v>50.35</v>
+      </c>
+      <c r="E65" s="7">
+        <v>74.038830000000004</v>
+      </c>
+      <c r="F65" s="5">
+        <v>11.0524</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B66" s="7">
+        <v>83.14</v>
+      </c>
+      <c r="C66" s="7">
+        <v>1.88</v>
+      </c>
+      <c r="D66" s="7">
+        <v>74.42</v>
+      </c>
+      <c r="E66" s="7">
+        <v>76.11824</v>
+      </c>
+      <c r="F66" s="5">
+        <v>84.392899999999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B67" s="7">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="C67" s="7">
+        <v>18.43</v>
+      </c>
+      <c r="D67" s="7">
+        <v>43.28</v>
+      </c>
+      <c r="E67" s="7">
+        <v>79.974720000000005</v>
+      </c>
+      <c r="F67" s="5">
+        <v>8.9933999999999994</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B68" s="7">
+        <v>70.66</v>
+      </c>
+      <c r="C68" s="7">
+        <v>16.27</v>
+      </c>
+      <c r="D68" s="7">
+        <v>59.3</v>
+      </c>
+      <c r="E68" s="7">
+        <v>80.083420000000004</v>
+      </c>
+      <c r="F68" s="5">
+        <v>10.960699999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" s="7">
+        <v>75.95</v>
+      </c>
+      <c r="C69" s="7">
+        <v>5.72</v>
+      </c>
+      <c r="D69" s="7">
+        <v>60.16</v>
+      </c>
+      <c r="E69" s="7">
+        <v>81.344729999999998</v>
+      </c>
+      <c r="F69" s="5">
+        <v>30.5215</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" s="7">
+        <v>74.19</v>
+      </c>
+      <c r="C70" s="7">
+        <v>22.69</v>
+      </c>
+      <c r="D70" s="7">
+        <v>47.45</v>
+      </c>
+      <c r="E70" s="7">
+        <v>84.871790000000004</v>
+      </c>
+      <c r="F70" s="5">
+        <v>10.133800000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="7">
+        <v>76.23</v>
+      </c>
+      <c r="C71" s="7">
+        <v>9.75</v>
+      </c>
+      <c r="D71" s="7">
+        <v>49.95</v>
+      </c>
+      <c r="E71" s="7">
+        <v>87.983329999999995</v>
+      </c>
+      <c r="F71" s="5">
+        <v>14.847200000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72" s="7">
+        <v>73.97</v>
+      </c>
+      <c r="C72" s="7">
+        <v>16.309999999999999</v>
+      </c>
+      <c r="D72" s="7">
+        <v>44.83</v>
+      </c>
+      <c r="E72" s="7">
+        <v>92.033649999999994</v>
+      </c>
+      <c r="F72" s="5">
+        <v>14.7935</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" s="7">
+        <v>79.209999999999994</v>
+      </c>
+      <c r="C73" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="D73" s="7">
+        <v>59.42</v>
+      </c>
+      <c r="E73" s="7">
+        <v>93.480450000000005</v>
+      </c>
+      <c r="F73" s="5">
+        <v>29.537600000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" s="7">
+        <v>71.959999999999994</v>
+      </c>
+      <c r="C74" s="7">
+        <v>6.31</v>
+      </c>
+      <c r="D74" s="7">
+        <v>51.08</v>
+      </c>
+      <c r="E74" s="7">
+        <v>93.833119999999994</v>
+      </c>
+      <c r="F74" s="5">
+        <v>33.941499999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" s="7">
+        <v>69.63</v>
+      </c>
+      <c r="C75" s="7">
+        <v>25.63</v>
+      </c>
+      <c r="D75" s="7">
+        <v>49.98</v>
+      </c>
+      <c r="E75" s="7">
+        <v>95.81711</v>
+      </c>
+      <c r="F75" s="5">
+        <v>7.3418999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F1 B1:E75">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>#N/A</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="#Н/Д">
+      <formula>NOT(ISERROR(SEARCH("#Н/Д",B1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C7A589-E8F6-404B-9561-7F098E1C5944}">
   <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -3374,7 +4913,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -3397,7 +4936,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>95</v>
       </c>
@@ -3420,7 +4959,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -3443,7 +4982,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>109</v>
       </c>
@@ -3466,7 +5005,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
@@ -3489,7 +5028,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -3512,7 +5051,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>130</v>
       </c>
@@ -3535,7 +5074,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>137</v>
       </c>
@@ -3558,7 +5097,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>144</v>
       </c>
@@ -3581,7 +5120,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>151</v>
       </c>
@@ -3604,7 +5143,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>158</v>
       </c>
@@ -3627,7 +5166,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>165</v>
       </c>
@@ -3650,7 +5189,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>172</v>
       </c>
@@ -3673,7 +5212,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>179</v>
       </c>
@@ -3696,7 +5235,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>186</v>
       </c>
@@ -3719,7 +5258,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>193</v>
       </c>
@@ -3742,7 +5281,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>200</v>
       </c>
@@ -3765,7 +5304,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>207</v>
       </c>
@@ -3788,7 +5327,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>214</v>
       </c>
@@ -3811,7 +5350,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>221</v>
       </c>
@@ -3834,7 +5373,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>228</v>
       </c>
@@ -3857,7 +5396,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>235</v>
       </c>
@@ -3880,7 +5419,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>242</v>
       </c>
@@ -3903,7 +5442,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>249</v>
       </c>
@@ -3926,7 +5465,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>256</v>
       </c>
@@ -3949,7 +5488,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>263</v>
       </c>
@@ -3972,7 +5511,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>270</v>
       </c>
@@ -3995,7 +5534,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>277</v>
       </c>
@@ -4018,7 +5557,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>284</v>
       </c>
@@ -4041,7 +5580,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>291</v>
       </c>
@@ -4064,7 +5603,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>298</v>
       </c>
@@ -4092,16 +5631,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{887C7891-F92E-4B59-B74C-21306C6E622E}">
   <dimension ref="A1:B193"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4109,7 +5648,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>81</v>
       </c>
@@ -4117,7 +5656,7 @@
         <v>5.3277999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -4125,7 +5664,7 @@
         <v>5.9687000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>95</v>
       </c>
@@ -4133,7 +5672,7 @@
         <v>14.6318</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -4141,7 +5680,7 @@
         <v>62.271299999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>109</v>
       </c>
@@ -4149,7 +5688,7 @@
         <v>81.219700000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
@@ -4157,7 +5696,7 @@
         <v>25.9162</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>123</v>
       </c>
@@ -4165,7 +5704,7 @@
         <v>9.0876999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>130</v>
       </c>
@@ -4173,7 +5712,7 @@
         <v>28.711099999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>137</v>
       </c>
@@ -4181,7 +5720,7 @@
         <v>70.7727</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>144</v>
       </c>
@@ -4189,7 +5728,7 @@
         <v>78.695599999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>151</v>
       </c>
@@ -4197,7 +5736,7 @@
         <v>22.536300000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>158</v>
       </c>
@@ -4205,7 +5744,7 @@
         <v>2.6089000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>165</v>
       </c>
@@ -4213,7 +5752,7 @@
         <v>68.418599999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>172</v>
       </c>
@@ -4221,7 +5760,7 @@
         <v>5.0122999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -4229,7 +5768,7 @@
         <v>4.5778999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>186</v>
       </c>
@@ -4237,7 +5776,7 @@
         <v>6.4966999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>193</v>
       </c>
@@ -4245,7 +5784,7 @@
         <v>30.1493</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>200</v>
       </c>
@@ -4253,7 +5792,7 @@
         <v>55.454599999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>207</v>
       </c>
@@ -4261,7 +5800,7 @@
         <v>31.993500000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>214</v>
       </c>
@@ -4269,7 +5808,7 @@
         <v>31.035900000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>221</v>
       </c>
@@ -4277,7 +5816,7 @@
         <v>20.405799999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>228</v>
       </c>
@@ -4285,7 +5824,7 @@
         <v>20.471800000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>235</v>
       </c>
@@ -4293,7 +5832,7 @@
         <v>22.1584</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>242</v>
       </c>
@@ -4301,7 +5840,7 @@
         <v>24.1099</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>249</v>
       </c>
@@ -4309,7 +5848,7 @@
         <v>18.238900000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>256</v>
       </c>
@@ -4317,7 +5856,7 @@
         <v>80.4298</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>263</v>
       </c>
@@ -4325,7 +5864,7 @@
         <v>14.3771</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>270</v>
       </c>
@@ -4333,7 +5872,7 @@
         <v>12.5594</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>277</v>
       </c>
@@ -4341,7 +5880,7 @@
         <v>2.8851</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>284</v>
       </c>
@@ -4349,7 +5888,7 @@
         <v>73.565700000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>291</v>
       </c>
@@ -4357,7 +5896,7 @@
         <v>87.454700000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>298</v>
       </c>
@@ -4365,7 +5904,7 @@
         <v>29.503399999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>81</v>
       </c>
@@ -4373,7 +5912,7 @@
         <v>5.0410000000000004</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>88</v>
       </c>
@@ -4381,7 +5920,7 @@
         <v>5.4511000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>95</v>
       </c>
@@ -4389,7 +5928,7 @@
         <v>14.847200000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>102</v>
       </c>
@@ -4397,7 +5936,7 @@
         <v>54.659300000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>109</v>
       </c>
@@ -4405,7 +5944,7 @@
         <v>77.561099999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>116</v>
       </c>
@@ -4413,7 +5952,7 @@
         <v>23.237500000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -4421,7 +5960,7 @@
         <v>8.5898000000000003</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>130</v>
       </c>
@@ -4429,7 +5968,7 @@
         <v>23.171399999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>137</v>
       </c>
@@ -4437,7 +5976,7 @@
         <v>69.8215</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>144</v>
       </c>
@@ -4445,7 +5984,7 @@
         <v>78.899900000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>151</v>
       </c>
@@ -4453,7 +5992,7 @@
         <v>21.442699999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>158</v>
       </c>
@@ -4461,7 +6000,7 @@
         <v>2.6171000000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>165</v>
       </c>
@@ -4469,7 +6008,7 @@
         <v>68.1417</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>172</v>
       </c>
@@ -4477,7 +6016,7 @@
         <v>5.1379999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>179</v>
       </c>
@@ -4485,7 +6024,7 @@
         <v>4.5247000000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>186</v>
       </c>
@@ -4493,7 +6032,7 @@
         <v>6.8183999999999996</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>193</v>
       </c>
@@ -4501,7 +6040,7 @@
         <v>33.941499999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>200</v>
       </c>
@@ -4509,7 +6048,7 @@
         <v>52.585900000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>207</v>
       </c>
@@ -4517,7 +6056,7 @@
         <v>25.4894</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>214</v>
       </c>
@@ -4525,7 +6064,7 @@
         <v>30.5215</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>221</v>
       </c>
@@ -4533,7 +6072,7 @@
         <v>20.5472</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>228</v>
       </c>
@@ -4541,7 +6080,7 @@
         <v>17.4009</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>235</v>
       </c>
@@ -4549,7 +6088,7 @@
         <v>22.1432</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>242</v>
       </c>
@@ -4557,7 +6096,7 @@
         <v>24.020399999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>249</v>
       </c>
@@ -4565,7 +6104,7 @@
         <v>15.466200000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>256</v>
       </c>
@@ -4573,7 +6112,7 @@
         <v>80.482699999999994</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>263</v>
       </c>
@@ -4581,7 +6120,7 @@
         <v>15.5166</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>270</v>
       </c>
@@ -4589,7 +6128,7 @@
         <v>11.299300000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>277</v>
       </c>
@@ -4597,7 +6136,7 @@
         <v>2.8182</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>284</v>
       </c>
@@ -4605,7 +6144,7 @@
         <v>77.792000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>291</v>
       </c>
@@ -4613,7 +6152,7 @@
         <v>88.412300000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>298</v>
       </c>
@@ -4621,7 +6160,7 @@
         <v>29.537600000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>81</v>
       </c>
@@ -4629,7 +6168,7 @@
         <v>3.9024999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>88</v>
       </c>
@@ -4637,7 +6176,7 @@
         <v>5.3437000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>95</v>
       </c>
@@ -4645,7 +6184,7 @@
         <v>16.329499999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>102</v>
       </c>
@@ -4653,7 +6192,7 @@
         <v>58.445599999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>109</v>
       </c>
@@ -4661,7 +6200,7 @@
         <v>79.466899999999995</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>116</v>
       </c>
@@ -4669,7 +6208,7 @@
         <v>25.595800000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>123</v>
       </c>
@@ -4677,7 +6216,7 @@
         <v>8.9415999999999993</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>130</v>
       </c>
@@ -4685,7 +6224,7 @@
         <v>24.928699999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>137</v>
       </c>
@@ -4693,7 +6232,7 @@
         <v>71.1952</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>144</v>
       </c>
@@ -4701,7 +6240,7 @@
         <v>78.753699999999995</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>151</v>
       </c>
@@ -4709,7 +6248,7 @@
         <v>22.5474</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>158</v>
       </c>
@@ -4717,7 +6256,7 @@
         <v>2.6257000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>165</v>
       </c>
@@ -4725,7 +6264,7 @@
         <v>70.838200000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -4733,7 +6272,7 @@
         <v>5.2667999999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>179</v>
       </c>
@@ -4741,7 +6280,7 @@
         <v>4.4721000000000002</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>186</v>
       </c>
@@ -4749,7 +6288,7 @@
         <v>7.1558999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>193</v>
       </c>
@@ -4757,7 +6296,7 @@
         <v>33.483400000000003</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>200</v>
       </c>
@@ -4765,7 +6304,7 @@
         <v>53.700299999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>207</v>
       </c>
@@ -4773,7 +6312,7 @@
         <v>29.933599999999998</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>214</v>
       </c>
@@ -4781,7 +6320,7 @@
         <v>33.326900000000002</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>221</v>
       </c>
@@ -4789,7 +6328,7 @@
         <v>21.223400000000002</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>228</v>
       </c>
@@ -4797,7 +6336,7 @@
         <v>20.253900000000002</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>235</v>
       </c>
@@ -4805,7 +6344,7 @@
         <v>22.0928</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>242</v>
       </c>
@@ -4813,7 +6352,7 @@
         <v>21.8979</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>249</v>
       </c>
@@ -4821,7 +6360,7 @@
         <v>15.402200000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>256</v>
       </c>
@@ -4829,7 +6368,7 @@
         <v>78.445499999999996</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>263</v>
       </c>
@@ -4837,7 +6376,7 @@
         <v>16.746400000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>270</v>
       </c>
@@ -4845,7 +6384,7 @@
         <v>12.458500000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>277</v>
       </c>
@@ -4853,7 +6392,7 @@
         <v>2.7528999999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>284</v>
       </c>
@@ -4861,7 +6400,7 @@
         <v>81.965699999999998</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>291</v>
       </c>
@@ -4869,7 +6408,7 @@
         <v>89.507599999999996</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>298</v>
       </c>
@@ -4877,7 +6416,7 @@
         <v>31.110800000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>81</v>
       </c>
@@ -4885,7 +6424,7 @@
         <v>3.6067999999999998</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>88</v>
       </c>
@@ -4893,7 +6432,7 @@
         <v>5.3361000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>95</v>
       </c>
@@ -4901,7 +6440,7 @@
         <v>17.327100000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>102</v>
       </c>
@@ -4909,7 +6448,7 @@
         <v>62.958300000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>109</v>
       </c>
@@ -4917,7 +6456,7 @@
         <v>81.196100000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>116</v>
       </c>
@@ -4925,7 +6464,7 @@
         <v>26.887899999999998</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>123</v>
       </c>
@@ -4933,7 +6472,7 @@
         <v>8.8646999999999991</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>130</v>
       </c>
@@ -4941,7 +6480,7 @@
         <v>27.055299999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>137</v>
       </c>
@@ -4949,7 +6488,7 @@
         <v>73.277000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>144</v>
       </c>
@@ -4957,7 +6496,7 @@
         <v>82.426699999999997</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -4965,7 +6504,7 @@
         <v>23.601099999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>158</v>
       </c>
@@ -4973,7 +6512,7 @@
         <v>2.6029</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>165</v>
       </c>
@@ -4981,7 +6520,7 @@
         <v>68.391199999999998</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>172</v>
       </c>
@@ -4989,7 +6528,7 @@
         <v>5.4554</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>179</v>
       </c>
@@ -4997,7 +6536,7 @@
         <v>4.4353999999999996</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>186</v>
       </c>
@@ -5005,7 +6544,7 @@
         <v>7.5102000000000002</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>193</v>
       </c>
@@ -5013,7 +6552,7 @@
         <v>35.410600000000002</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>200</v>
       </c>
@@ -5021,7 +6560,7 @@
         <v>56.258899999999997</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>207</v>
       </c>
@@ -5029,7 +6568,7 @@
         <v>33.092399999999998</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>214</v>
       </c>
@@ -5037,7 +6576,7 @@
         <v>35.170299999999997</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>221</v>
       </c>
@@ -5045,7 +6584,7 @@
         <v>20.398099999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>228</v>
       </c>
@@ -5053,7 +6592,7 @@
         <v>21.801600000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>235</v>
       </c>
@@ -5061,7 +6600,7 @@
         <v>21.719799999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>242</v>
       </c>
@@ -5069,7 +6608,7 @@
         <v>24.361000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>249</v>
       </c>
@@ -5077,7 +6616,7 @@
         <v>18.137799999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>256</v>
       </c>
@@ -5085,7 +6624,7 @@
         <v>76.549800000000005</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>263</v>
       </c>
@@ -5093,7 +6632,7 @@
         <v>18.073699999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>270</v>
       </c>
@@ -5101,7 +6640,7 @@
         <v>12.934900000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>277</v>
       </c>
@@ -5109,7 +6648,7 @@
         <v>2.7730000000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>284</v>
       </c>
@@ -5117,7 +6656,7 @@
         <v>83.872600000000006</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>291</v>
       </c>
@@ -5125,7 +6664,7 @@
         <v>91.469899999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>298</v>
       </c>
@@ -5133,7 +6672,7 @@
         <v>32.767800000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>81</v>
       </c>
@@ -5141,7 +6680,7 @@
         <v>3.6107</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>88</v>
       </c>
@@ -5149,7 +6688,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>95</v>
       </c>
@@ -5157,7 +6696,7 @@
         <v>18.217199999999998</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>102</v>
       </c>
@@ -5165,7 +6704,7 @@
         <v>63.665500000000002</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>109</v>
       </c>
@@ -5173,7 +6712,7 @@
         <v>80.853899999999996</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>116</v>
       </c>
@@ -5181,7 +6720,7 @@
         <v>26.378900000000002</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>123</v>
       </c>
@@ -5189,7 +6728,7 @@
         <v>8.8484999999999996</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>130</v>
       </c>
@@ -5197,7 +6736,7 @@
         <v>27.570699999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -5205,7 +6744,7 @@
         <v>73.983599999999996</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>144</v>
       </c>
@@ -5213,7 +6752,7 @@
         <v>80.835800000000006</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>151</v>
       </c>
@@ -5221,7 +6760,7 @@
         <v>23.891999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>158</v>
       </c>
@@ -5229,7 +6768,7 @@
         <v>2.6004</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>165</v>
       </c>
@@ -5237,7 +6776,7 @@
         <v>68.583500000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>172</v>
       </c>
@@ -5245,7 +6784,7 @@
         <v>5.6574</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>179</v>
       </c>
@@ -5253,7 +6792,7 @@
         <v>4.4642999999999997</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>186</v>
       </c>
@@ -5261,7 +6800,7 @@
         <v>7.8475000000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>193</v>
       </c>
@@ -5269,7 +6808,7 @@
         <v>36.182299999999998</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>200</v>
       </c>
@@ -5277,7 +6816,7 @@
         <v>56.500100000000003</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>207</v>
       </c>
@@ -5285,7 +6824,7 @@
         <v>33.938899999999997</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>214</v>
       </c>
@@ -5293,7 +6832,7 @@
         <v>36.093899999999998</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>221</v>
       </c>
@@ -5301,7 +6840,7 @@
         <v>21.355</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>228</v>
       </c>
@@ -5309,7 +6848,7 @@
         <v>21.603000000000002</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>235</v>
       </c>
@@ -5317,7 +6856,7 @@
         <v>22.932400000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>242</v>
       </c>
@@ -5325,7 +6864,7 @@
         <v>25.532699999999998</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>249</v>
       </c>
@@ -5333,7 +6872,7 @@
         <v>18.879200000000001</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>256</v>
       </c>
@@ -5341,7 +6880,7 @@
         <v>76.809299999999993</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>263</v>
       </c>
@@ -5349,7 +6888,7 @@
         <v>18.824300000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>270</v>
       </c>
@@ -5357,7 +6896,7 @@
         <v>13.1327</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>277</v>
       </c>
@@ -5365,7 +6904,7 @@
         <v>2.7629999999999999</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>284</v>
       </c>
@@ -5373,7 +6912,7 @@
         <v>82.716899999999995</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>291</v>
       </c>
@@ -5381,7 +6920,7 @@
         <v>90.944800000000001</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>298</v>
       </c>
@@ -5389,7 +6928,7 @@
         <v>32.761400000000002</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>81</v>
       </c>
@@ -5397,7 +6936,7 @@
         <v>3.7065999999999999</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>88</v>
       </c>
@@ -5405,7 +6944,7 @@
         <v>5.2976000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>95</v>
       </c>
@@ -5413,7 +6952,7 @@
         <v>19.157699999999998</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>102</v>
       </c>
@@ -5421,7 +6960,7 @@
         <v>64.943100000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>109</v>
       </c>
@@ -5429,7 +6968,7 @@
         <v>80.862300000000005</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>116</v>
       </c>
@@ -5437,7 +6976,7 @@
         <v>25.835899999999999</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>123</v>
       </c>
@@ -5445,7 +6984,7 @@
         <v>9.1568000000000005</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>130</v>
       </c>
@@ -5453,7 +6992,7 @@
         <v>28.623899999999999</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>137</v>
       </c>
@@ -5461,7 +7000,7 @@
         <v>73.5197</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>144</v>
       </c>
@@ -5469,7 +7008,7 @@
         <v>79.480500000000006</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>151</v>
       </c>
@@ -5477,7 +7016,7 @@
         <v>24.7456</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>158</v>
       </c>
@@ -5485,7 +7024,7 @@
         <v>2.6225000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>165</v>
       </c>
@@ -5493,7 +7032,7 @@
         <v>68.7607</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>172</v>
       </c>
@@ -5501,7 +7040,7 @@
         <v>5.9313000000000002</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>179</v>
       </c>
@@ -5509,7 +7048,7 @@
         <v>4.5827</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>186</v>
       </c>
@@ -5517,7 +7056,7 @@
         <v>8.0801999999999996</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>193</v>
       </c>
@@ -5525,7 +7064,7 @@
         <v>37.212200000000003</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>200</v>
       </c>
@@ -5533,7 +7072,7 @@
         <v>57.779499999999999</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>207</v>
       </c>
@@ -5541,7 +7080,7 @@
         <v>34.924399999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>214</v>
       </c>
@@ -5549,7 +7088,7 @@
         <v>37.232399999999998</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>221</v>
       </c>
@@ -5557,7 +7096,7 @@
         <v>22.319800000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>228</v>
       </c>
@@ -5565,7 +7104,7 @@
         <v>23.029800000000002</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>235</v>
       </c>
@@ -5573,7 +7112,7 @@
         <v>22.9331</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>242</v>
       </c>
@@ -5581,7 +7120,7 @@
         <v>26.292899999999999</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>249</v>
       </c>
@@ -5589,7 +7128,7 @@
         <v>19.587499999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>256</v>
       </c>
@@ -5597,7 +7136,7 @@
         <v>79.383099999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>263</v>
       </c>
@@ -5605,7 +7144,7 @@
         <v>19.929400000000001</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>270</v>
       </c>
@@ -5613,7 +7152,7 @@
         <v>12.5334</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>277</v>
       </c>
@@ -5621,7 +7160,7 @@
         <v>2.7117</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>284</v>
       </c>
@@ -5629,7 +7168,7 @@
         <v>81.529700000000005</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>291</v>
       </c>
@@ -5637,7 +7176,7 @@
         <v>90.640199999999993</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>298</v>
       </c>
